--- a/data/publications/handbook-statistics-on-indian-economy/annual-series/output-and-prices/Pattern of Land Use and Select Inputs for Agricultural Production.xlsx
+++ b/data/publications/handbook-statistics-on-indian-economy/annual-series/output-and-prices/Pattern of Land Use and Select Inputs for Agricultural Production.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="87">
   <si>
     <t>Year</t>
   </si>
@@ -34,12 +34,15 @@
     <t>Consumption of Pesticides (Technical Grade Material) ('000 tonnes)</t>
   </si>
   <si>
+    <t xml:space="preserve">2024-25   </t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
     <t xml:space="preserve">2023-24   </t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t xml:space="preserve">2022-23   </t>
   </si>
   <si>
@@ -265,12 +268,11 @@
     <t>(Area in Lakhs Hectares)</t>
   </si>
   <si>
-    <t xml:space="preserve">Notes :  N : Nitrogen, P : Phosphorus, K : Potassium.
-             1. Data of Net Sown Area, Gross Sown Area, Net Irrigated Area and Gross Irrigated Area for 2003-04 onwards are provisional.
-             2. Consumption of Fertilizer data relate to February-January upto 1982-83 and April-March from 1983-84 onwards.
-             3. - : Not Available.
-Also see Notes on Tables.
-Source : Ministry of Agriculture &amp; Farmers Welfare, Government of India</t>
+    <t xml:space="preserve">Notes : N : Nitrogen, P : Phosphorus, K : Potassium 
+             1. Consumption of Fertilizer data relate to February-January upto 1982-83 and April-March from 1983-84 onwards.
+             2. - : Not Available.
+                Also see Notes on Tables.
+Source : Ministry of Agriculture &amp; Farmers Welfare, Government of India.</t>
   </si>
 </sst>
 </file>
@@ -442,10 +444,10 @@
     <xf numFmtId="49" fontId="3" fillId="4" borderId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="4" fillId="2" borderId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="4" fillId="4" borderId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="5" fillId="2" borderId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="5" fillId="4" borderId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="2" borderId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -463,19 +465,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:K85"/>
   <cols>
     <col min="1" max="1" width="4.67767866666667" customWidth="1"/>
     <col min="2" max="2" width="9.636356" customWidth="1"/>
     <col min="3" max="9" width="14.7053106666667" customWidth="1"/>
     <col min="10" max="10" width="14.3668733333333" customWidth="1"/>
     <col min="11" max="11" width="17.1276093333333" customWidth="1"/>
+    <col min="12" max="12" width="4.67767866666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
     <row r="2" s="1" customFormat="1" ht="17.0656" customHeight="1">
       <c r="B2" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
@@ -490,7 +493,7 @@
     <row r="3" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
     <row r="4" s="1" customFormat="1" ht="12.7992" customHeight="1">
       <c r="B4" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C4" s="13"/>
     </row>
@@ -552,22 +555,22 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>1389.9</v>
+        <v>1413.7</v>
       </c>
       <c r="D8" s="5">
-        <v>2178.8</v>
+        <v>2257.9</v>
       </c>
       <c r="E8" s="5">
-        <v>824.2</v>
+        <v>845</v>
       </c>
       <c r="F8" s="5">
-        <v>1305.5</v>
+        <v>1369.1</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H8" s="5">
-        <v>306.42</v>
+        <v>329.28</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>9</v>
@@ -578,25 +581,25 @@
         <v>10</v>
       </c>
       <c r="C9" s="7">
-        <v>1407.1</v>
+        <v>1391.6</v>
       </c>
       <c r="D9" s="7">
-        <v>2193.6</v>
+        <v>2179.2</v>
       </c>
       <c r="E9" s="7">
-        <v>793.1</v>
+        <v>824.2</v>
       </c>
       <c r="F9" s="7">
-        <v>1222.9</v>
+        <v>1305.5</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>9</v>
       </c>
       <c r="H9" s="7">
-        <v>298.44</v>
+        <v>306.42</v>
       </c>
       <c r="I9" s="8">
-        <v>53.63</v>
+        <v>67.96</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -604,25 +607,25 @@
         <v>11</v>
       </c>
       <c r="C10" s="5">
-        <v>1410.1</v>
+        <v>1407.1</v>
       </c>
       <c r="D10" s="5">
-        <v>2191.6</v>
+        <v>2193.6</v>
       </c>
       <c r="E10" s="5">
-        <v>779.2</v>
+        <v>793.1</v>
       </c>
       <c r="F10" s="5">
-        <v>1203.8</v>
+        <v>1222.9</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H10" s="5">
-        <v>297.96</v>
+        <v>298.44</v>
       </c>
       <c r="I10" s="6">
-        <v>58.7</v>
+        <v>64.51</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -630,25 +633,25 @@
         <v>12</v>
       </c>
       <c r="C11" s="7">
-        <v>1415.4</v>
+        <v>1410.1</v>
       </c>
       <c r="D11" s="7">
-        <v>2161.1</v>
+        <v>2191.6</v>
       </c>
       <c r="E11" s="7">
-        <v>777.3</v>
+        <v>779.2</v>
       </c>
       <c r="F11" s="7">
-        <v>1189.3</v>
+        <v>1203.8</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>9</v>
       </c>
       <c r="H11" s="7">
-        <v>325.4</v>
+        <v>297.96</v>
       </c>
       <c r="I11" s="8">
-        <v>62.2</v>
+        <v>69.89</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -656,25 +659,25 @@
         <v>13</v>
       </c>
       <c r="C12" s="5">
-        <v>1399</v>
+        <v>1415.4</v>
       </c>
       <c r="D12" s="5">
-        <v>2113.6</v>
+        <v>2161.1</v>
       </c>
       <c r="E12" s="5">
-        <v>754.7</v>
+        <v>777.3</v>
       </c>
       <c r="F12" s="5">
-        <v>1124.4</v>
+        <v>1189.3</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H12" s="5">
-        <v>293.7</v>
+        <v>325.4</v>
       </c>
       <c r="I12" s="6">
-        <v>61.7</v>
+        <v>62.19</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -682,25 +685,25 @@
         <v>14</v>
       </c>
       <c r="C13" s="7">
-        <v>1384.4</v>
+        <v>1399</v>
       </c>
       <c r="D13" s="7">
-        <v>2011.8</v>
+        <v>2113.6</v>
       </c>
       <c r="E13" s="7">
-        <v>722.4</v>
+        <v>754.7</v>
       </c>
       <c r="F13" s="7">
-        <v>1047.1</v>
+        <v>1124.4</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>9</v>
       </c>
       <c r="H13" s="7">
-        <v>273.8</v>
+        <v>293.7</v>
       </c>
       <c r="I13" s="8">
-        <v>59.67</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -708,25 +711,25 @@
         <v>15</v>
       </c>
       <c r="C14" s="5">
-        <v>1387.7</v>
+        <v>1384.4</v>
       </c>
       <c r="D14" s="5">
-        <v>2008.8</v>
+        <v>2011.8</v>
       </c>
       <c r="E14" s="5">
-        <v>701.6</v>
+        <v>722.4</v>
       </c>
       <c r="F14" s="5">
-        <v>1014.7</v>
+        <v>1047.1</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H14" s="5">
-        <v>265.9</v>
+        <v>273.8</v>
       </c>
       <c r="I14" s="6">
-        <v>63.41</v>
+        <v>59.67</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -734,25 +737,25 @@
         <v>16</v>
       </c>
       <c r="C15" s="7">
-        <v>1390</v>
+        <v>1387.7</v>
       </c>
       <c r="D15" s="7">
-        <v>2011.6</v>
+        <v>2008.8</v>
       </c>
       <c r="E15" s="7">
-        <v>692.7</v>
+        <v>701.6</v>
       </c>
       <c r="F15" s="7">
-        <v>996.2</v>
+        <v>1014.7</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>9</v>
       </c>
       <c r="H15" s="7">
-        <v>259.5</v>
+        <v>265.9</v>
       </c>
       <c r="I15" s="8">
-        <v>58.63</v>
+        <v>63.41</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -760,25 +763,25 @@
         <v>17</v>
       </c>
       <c r="C16" s="5">
-        <v>1389.7</v>
+        <v>1390</v>
       </c>
       <c r="D16" s="5">
-        <v>1981.2</v>
+        <v>2011.6</v>
       </c>
       <c r="E16" s="5">
-        <v>677.7</v>
+        <v>692.7</v>
       </c>
       <c r="F16" s="5">
-        <v>977.5</v>
+        <v>996.2</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H16" s="5">
-        <v>267.5</v>
+        <v>259.5</v>
       </c>
       <c r="I16" s="6">
-        <v>56.72</v>
+        <v>58.63</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -786,25 +789,25 @@
         <v>18</v>
       </c>
       <c r="C17" s="7">
-        <v>1394.5</v>
+        <v>1389.7</v>
       </c>
       <c r="D17" s="7">
-        <v>1982.8</v>
+        <v>1981.2</v>
       </c>
       <c r="E17" s="7">
-        <v>685.8</v>
+        <v>677.7</v>
       </c>
       <c r="F17" s="7">
-        <v>978.5</v>
+        <v>977.5</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>9</v>
       </c>
       <c r="H17" s="7">
-        <v>255.8</v>
+        <v>267.5</v>
       </c>
       <c r="I17" s="8">
-        <v>56.27</v>
+        <v>56.72</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -812,25 +815,25 @@
         <v>19</v>
       </c>
       <c r="C18" s="5">
-        <v>1412.4</v>
+        <v>1394.5</v>
       </c>
       <c r="D18" s="5">
-        <v>2013</v>
+        <v>1982.8</v>
       </c>
       <c r="E18" s="5">
-        <v>684.2</v>
+        <v>685.8</v>
       </c>
       <c r="F18" s="5">
-        <v>962.7</v>
+        <v>978.5</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H18" s="5">
-        <v>244.8</v>
+        <v>255.8</v>
       </c>
       <c r="I18" s="6">
-        <v>60.28</v>
+        <v>56.27</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -838,25 +841,25 @@
         <v>20</v>
       </c>
       <c r="C19" s="7">
-        <v>1397.5</v>
+        <v>1412.4</v>
       </c>
       <c r="D19" s="7">
-        <v>1944.6</v>
+        <v>2013</v>
       </c>
       <c r="E19" s="7">
-        <v>665.9</v>
+        <v>684.2</v>
       </c>
       <c r="F19" s="7">
-        <v>927.8</v>
+        <v>962.7</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>9</v>
       </c>
       <c r="H19" s="7">
-        <v>255.4</v>
+        <v>244.8</v>
       </c>
       <c r="I19" s="8">
-        <v>45.62</v>
+        <v>60.28</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -864,25 +867,25 @@
         <v>21</v>
       </c>
       <c r="C20" s="5">
-        <v>1407.9</v>
+        <v>1397.5</v>
       </c>
       <c r="D20" s="5">
-        <v>1955.5</v>
+        <v>1944.6</v>
       </c>
       <c r="E20" s="5">
-        <v>660.1</v>
+        <v>665.9</v>
       </c>
       <c r="F20" s="5">
-        <v>919.3</v>
+        <v>927.8</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H20" s="5">
-        <v>277.9</v>
+        <v>255.4</v>
       </c>
       <c r="I20" s="6">
-        <v>52.98</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -890,25 +893,25 @@
         <v>22</v>
       </c>
       <c r="C21" s="7">
-        <v>1413.7</v>
+        <v>1407.9</v>
       </c>
       <c r="D21" s="7">
-        <v>1981.3</v>
+        <v>1955.5</v>
       </c>
       <c r="E21" s="7">
-        <v>638.7</v>
+        <v>660.1</v>
       </c>
       <c r="F21" s="7">
-        <v>893.2</v>
+        <v>919.3</v>
       </c>
       <c r="G21" s="7" t="s">
         <v>9</v>
       </c>
       <c r="H21" s="7">
-        <v>281.2</v>
+        <v>277.9</v>
       </c>
       <c r="I21" s="8">
-        <v>55.5</v>
+        <v>52.98</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -916,25 +919,25 @@
         <v>23</v>
       </c>
       <c r="C22" s="5">
-        <v>1391.73</v>
+        <v>1413.7</v>
       </c>
       <c r="D22" s="5">
-        <v>1891.88</v>
+        <v>1981.3</v>
       </c>
       <c r="E22" s="5">
-        <v>619.45</v>
+        <v>638.7</v>
       </c>
       <c r="F22" s="5">
-        <v>850.87</v>
+        <v>893.2</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H22" s="5">
-        <v>264.86</v>
+        <v>281.2</v>
       </c>
       <c r="I22" s="6">
-        <v>41.82</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -942,25 +945,25 @@
         <v>24</v>
       </c>
       <c r="C23" s="7">
-        <v>1419</v>
+        <v>1391.73</v>
       </c>
       <c r="D23" s="7">
-        <v>1953.3</v>
+        <v>1891.88</v>
       </c>
       <c r="E23" s="7">
-        <v>636.4</v>
+        <v>619.45</v>
       </c>
       <c r="F23" s="7">
-        <v>889</v>
+        <v>850.87</v>
       </c>
       <c r="G23" s="7" t="s">
         <v>9</v>
       </c>
       <c r="H23" s="7">
-        <v>249.09</v>
+        <v>264.86</v>
       </c>
       <c r="I23" s="8">
-        <v>43.86</v>
+        <v>41.82</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -968,25 +971,25 @@
         <v>25</v>
       </c>
       <c r="C24" s="5">
-        <v>1410.2</v>
+        <v>1419</v>
       </c>
       <c r="D24" s="5">
-        <v>1952.2</v>
+        <v>1953.3</v>
       </c>
       <c r="E24" s="5">
-        <v>631.9</v>
+        <v>636.4</v>
       </c>
       <c r="F24" s="5">
-        <v>880.6</v>
+        <v>889</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H24" s="5">
-        <v>225.7</v>
+        <v>249.09</v>
       </c>
       <c r="I24" s="6">
-        <v>41.6</v>
+        <v>43.86</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -994,25 +997,25 @@
         <v>26</v>
       </c>
       <c r="C25" s="7">
-        <v>1398.2</v>
+        <v>1410.2</v>
       </c>
       <c r="D25" s="7">
-        <v>1923.8</v>
+        <v>1952.2</v>
       </c>
       <c r="E25" s="7">
-        <v>627.4</v>
+        <v>631.9</v>
       </c>
       <c r="F25" s="7">
-        <v>867.5</v>
+        <v>880.6</v>
       </c>
       <c r="G25" s="7" t="s">
         <v>9</v>
       </c>
       <c r="H25" s="7">
-        <v>216.51</v>
+        <v>225.7</v>
       </c>
       <c r="I25" s="8">
-        <v>43.4</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1020,25 +1023,25 @@
         <v>27</v>
       </c>
       <c r="C26" s="5">
-        <v>1411.6</v>
+        <v>1398.2</v>
       </c>
       <c r="D26" s="5">
-        <v>1927.4</v>
+        <v>1923.8</v>
       </c>
       <c r="E26" s="5">
-        <v>608.4</v>
+        <v>627.4</v>
       </c>
       <c r="F26" s="5">
-        <v>842.8</v>
+        <v>867.5</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H26" s="5">
-        <v>203.4</v>
+        <v>216.51</v>
       </c>
       <c r="I26" s="6">
-        <v>39.77</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1046,25 +1049,25 @@
         <v>28</v>
       </c>
       <c r="C27" s="7">
-        <v>1406.4</v>
+        <v>1411.6</v>
       </c>
       <c r="D27" s="7">
-        <v>1911</v>
+        <v>1927.4</v>
       </c>
       <c r="E27" s="7">
-        <v>592.3</v>
+        <v>608.4</v>
       </c>
       <c r="F27" s="7">
-        <v>810.8</v>
+        <v>842.8</v>
       </c>
       <c r="G27" s="7" t="s">
         <v>9</v>
       </c>
       <c r="H27" s="7">
-        <v>183.98</v>
+        <v>203.4</v>
       </c>
       <c r="I27" s="8">
-        <v>40.67</v>
+        <v>39.77</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1072,25 +1075,25 @@
         <v>29</v>
       </c>
       <c r="C28" s="5">
-        <v>1407.1</v>
+        <v>1406.4</v>
       </c>
       <c r="D28" s="5">
-        <v>1896.6</v>
+        <v>1911</v>
       </c>
       <c r="E28" s="5">
-        <v>570.6</v>
+        <v>592.3</v>
       </c>
       <c r="F28" s="5">
-        <v>780.4</v>
+        <v>810.8</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H28" s="5">
-        <v>167.99</v>
+        <v>183.98</v>
       </c>
       <c r="I28" s="6">
-        <v>41</v>
+        <v>40.67</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1098,25 +1101,25 @@
         <v>30</v>
       </c>
       <c r="C29" s="7">
-        <v>1319.4</v>
+        <v>1407.1</v>
       </c>
       <c r="D29" s="7">
-        <v>1738.9</v>
+        <v>1896.6</v>
       </c>
       <c r="E29" s="7">
-        <v>539</v>
+        <v>570.6</v>
       </c>
       <c r="F29" s="7">
-        <v>730.6</v>
+        <v>780.4</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>9</v>
       </c>
       <c r="H29" s="7">
-        <v>160.94</v>
+        <v>167.99</v>
       </c>
       <c r="I29" s="8">
-        <v>48.3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1124,25 +1127,25 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>1407.3</v>
+        <v>1319.4</v>
       </c>
       <c r="D30" s="5">
-        <v>1880.1</v>
+        <v>1738.9</v>
       </c>
       <c r="E30" s="5">
-        <v>569.4</v>
+        <v>539</v>
       </c>
       <c r="F30" s="5">
-        <v>783.7</v>
+        <v>730.6</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H30" s="5">
-        <v>173.6</v>
+        <v>160.94</v>
       </c>
       <c r="I30" s="6">
-        <v>47.02</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1150,25 +1153,25 @@
         <v>32</v>
       </c>
       <c r="C31" s="7">
-        <v>1413.4</v>
+        <v>1407.3</v>
       </c>
       <c r="D31" s="7">
-        <v>1853.4</v>
+        <v>1880.1</v>
       </c>
       <c r="E31" s="7">
-        <v>552</v>
+        <v>569.4</v>
       </c>
       <c r="F31" s="7">
-        <v>761.9</v>
+        <v>783.7</v>
       </c>
       <c r="G31" s="7" t="s">
         <v>9</v>
       </c>
       <c r="H31" s="7">
-        <v>167.02</v>
+        <v>173.6</v>
       </c>
       <c r="I31" s="8">
-        <v>43.58</v>
+        <v>47.02</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1176,25 +1179,25 @@
         <v>33</v>
       </c>
       <c r="C32" s="5">
-        <v>1410.6</v>
+        <v>1413.4</v>
       </c>
       <c r="D32" s="5">
-        <v>1884</v>
+        <v>1853.4</v>
       </c>
       <c r="E32" s="5">
-        <v>575.3</v>
+        <v>552</v>
       </c>
       <c r="F32" s="5">
-        <v>792.2</v>
+        <v>761.9</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H32" s="5">
-        <v>180.7</v>
+        <v>167.02</v>
       </c>
       <c r="I32" s="6">
-        <v>46.2</v>
+        <v>43.58</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1202,25 +1205,25 @@
         <v>34</v>
       </c>
       <c r="C33" s="7">
-        <v>1427.5</v>
+        <v>1410.6</v>
       </c>
       <c r="D33" s="7">
-        <v>1916.5</v>
+        <v>1884</v>
       </c>
       <c r="E33" s="7">
-        <v>574.4</v>
+        <v>575.3</v>
       </c>
       <c r="F33" s="7">
-        <v>786.7</v>
-      </c>
-      <c r="G33" s="7">
-        <v>783.5</v>
+        <v>792.2</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>9</v>
       </c>
       <c r="H33" s="7">
-        <v>167.98</v>
+        <v>180.7</v>
       </c>
       <c r="I33" s="8">
-        <v>49.16</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1228,25 +1231,25 @@
         <v>35</v>
       </c>
       <c r="C34" s="5">
-        <v>1419.5</v>
+        <v>1427.5</v>
       </c>
       <c r="D34" s="5">
-        <v>1899.9</v>
+        <v>1916.5</v>
       </c>
       <c r="E34" s="5">
-        <v>552.1</v>
+        <v>574.4</v>
       </c>
       <c r="F34" s="5">
-        <v>756.7</v>
+        <v>786.7</v>
       </c>
       <c r="G34" s="5">
-        <v>760</v>
+        <v>783.5</v>
       </c>
       <c r="H34" s="5">
-        <v>161.88</v>
+        <v>167.98</v>
       </c>
       <c r="I34" s="6">
-        <v>52.24</v>
+        <v>49.16</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1254,25 +1257,25 @@
         <v>36</v>
       </c>
       <c r="C35" s="7">
-        <v>1429.3</v>
+        <v>1419.5</v>
       </c>
       <c r="D35" s="7">
-        <v>1895</v>
+        <v>1899.9</v>
       </c>
       <c r="E35" s="7">
-        <v>551.1</v>
+        <v>552.1</v>
       </c>
       <c r="F35" s="7">
-        <v>760.3</v>
+        <v>756.7</v>
       </c>
       <c r="G35" s="7">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="H35" s="7">
-        <v>143.08</v>
+        <v>161.88</v>
       </c>
       <c r="I35" s="8">
-        <v>56.11</v>
+        <v>52.24</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1280,25 +1283,25 @@
         <v>37</v>
       </c>
       <c r="C36" s="5">
-        <v>1422</v>
+        <v>1429.3</v>
       </c>
       <c r="D36" s="5">
-        <v>1874.7</v>
+        <v>1895</v>
       </c>
       <c r="E36" s="5">
-        <v>534</v>
+        <v>551.1</v>
       </c>
       <c r="F36" s="5">
-        <v>713.5</v>
+        <v>760.3</v>
       </c>
       <c r="G36" s="5">
-        <v>721.1</v>
+        <v>764</v>
       </c>
       <c r="H36" s="5">
-        <v>138.76</v>
+        <v>143.08</v>
       </c>
       <c r="I36" s="6">
-        <v>61.26</v>
+        <v>56.11</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1306,25 +1309,25 @@
         <v>38</v>
       </c>
       <c r="C37" s="7">
-        <v>1429.6</v>
+        <v>1422</v>
       </c>
       <c r="D37" s="7">
-        <v>1880.5</v>
+        <v>1874.7</v>
       </c>
       <c r="E37" s="7">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="F37" s="7">
-        <v>706.5</v>
+        <v>713.5</v>
       </c>
       <c r="G37" s="7">
-        <v>709.3</v>
+        <v>721.1</v>
       </c>
       <c r="H37" s="7">
-        <v>135.64</v>
+        <v>138.76</v>
       </c>
       <c r="I37" s="8">
-        <v>61.36</v>
+        <v>61.26</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1332,25 +1335,25 @@
         <v>39</v>
       </c>
       <c r="C38" s="5">
-        <v>1423.4</v>
+        <v>1429.6</v>
       </c>
       <c r="D38" s="5">
-        <v>1865.8</v>
+        <v>1880.5</v>
       </c>
       <c r="E38" s="5">
-        <v>513.4</v>
+        <v>530</v>
       </c>
       <c r="F38" s="5">
-        <v>682.6</v>
+        <v>706.5</v>
       </c>
       <c r="G38" s="5">
-        <v>669.9</v>
+        <v>709.3</v>
       </c>
       <c r="H38" s="5">
-        <v>123.66</v>
+        <v>135.64</v>
       </c>
       <c r="I38" s="6">
-        <v>63.65</v>
+        <v>61.36</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1358,25 +1361,25 @@
         <v>40</v>
       </c>
       <c r="C39" s="7">
-        <v>1427.2</v>
+        <v>1423.4</v>
       </c>
       <c r="D39" s="7">
-        <v>1857</v>
+        <v>1865.8</v>
       </c>
       <c r="E39" s="7">
-        <v>502.9</v>
+        <v>513.4</v>
       </c>
       <c r="F39" s="7">
-        <v>667.6</v>
+        <v>682.6</v>
       </c>
       <c r="G39" s="7">
-        <v>654</v>
+        <v>669.9</v>
       </c>
       <c r="H39" s="7">
-        <v>121.55</v>
+        <v>123.66</v>
       </c>
       <c r="I39" s="8">
-        <v>70.79</v>
+        <v>63.65</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1384,25 +1387,25 @@
         <v>41</v>
       </c>
       <c r="C40" s="5">
-        <v>1416.3</v>
+        <v>1427.2</v>
       </c>
       <c r="D40" s="5">
-        <v>1822.4</v>
+        <v>1857</v>
       </c>
       <c r="E40" s="5">
-        <v>498.7</v>
+        <v>502.9</v>
       </c>
       <c r="F40" s="5">
-        <v>656.8</v>
+        <v>667.6</v>
       </c>
       <c r="G40" s="5">
-        <v>647.1</v>
+        <v>654</v>
       </c>
       <c r="H40" s="5">
-        <v>127.28</v>
+        <v>121.55</v>
       </c>
       <c r="I40" s="6">
-        <v>72.13</v>
+        <v>70.79</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1410,25 +1413,25 @@
         <v>42</v>
       </c>
       <c r="C41" s="7">
-        <v>1430</v>
+        <v>1416.3</v>
       </c>
       <c r="D41" s="7">
-        <v>1857.4</v>
+        <v>1822.4</v>
       </c>
       <c r="E41" s="7">
-        <v>480.2</v>
+        <v>498.7</v>
       </c>
       <c r="F41" s="7">
-        <v>632</v>
+        <v>656.8</v>
       </c>
       <c r="G41" s="7">
-        <v>649.8</v>
+        <v>647.1</v>
       </c>
       <c r="H41" s="7">
-        <v>125.46</v>
+        <v>127.28</v>
       </c>
       <c r="I41" s="8">
-        <v>75</v>
+        <v>72.13</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1436,25 +1439,25 @@
         <v>43</v>
       </c>
       <c r="C42" s="5">
-        <v>1423.4</v>
+        <v>1430</v>
       </c>
       <c r="D42" s="5">
-        <v>1822.7</v>
+        <v>1857.4</v>
       </c>
       <c r="E42" s="5">
-        <v>467</v>
+        <v>480.2</v>
       </c>
       <c r="F42" s="5">
-        <v>618.5</v>
+        <v>632</v>
       </c>
       <c r="G42" s="5">
-        <v>611.7</v>
+        <v>649.8</v>
       </c>
       <c r="H42" s="5">
-        <v>115.68</v>
+        <v>125.46</v>
       </c>
       <c r="I42" s="6">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1462,25 +1465,25 @@
         <v>44</v>
       </c>
       <c r="C43" s="7">
-        <v>1418.9</v>
+        <v>1423.4</v>
       </c>
       <c r="D43" s="7">
-        <v>1822.8</v>
+        <v>1822.7</v>
       </c>
       <c r="E43" s="7">
-        <v>461.5</v>
+        <v>467</v>
       </c>
       <c r="F43" s="7">
-        <v>611.3</v>
+        <v>618.5</v>
       </c>
       <c r="G43" s="7">
-        <v>601.1</v>
+        <v>611.7</v>
       </c>
       <c r="H43" s="7">
-        <v>110.4</v>
+        <v>115.68</v>
       </c>
       <c r="I43" s="8">
-        <v>75.89</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1488,25 +1491,25 @@
         <v>45</v>
       </c>
       <c r="C44" s="5">
-        <v>1340.9</v>
+        <v>1418.9</v>
       </c>
       <c r="D44" s="5">
-        <v>1707.4</v>
+        <v>1822.8</v>
       </c>
       <c r="E44" s="5">
-        <v>428.9</v>
+        <v>461.5</v>
       </c>
       <c r="F44" s="5">
-        <v>560.4</v>
+        <v>611.3</v>
       </c>
       <c r="G44" s="5">
-        <v>541</v>
+        <v>601.1</v>
       </c>
       <c r="H44" s="5">
-        <v>87.84</v>
+        <v>110.4</v>
       </c>
       <c r="I44" s="6">
-        <v>66.9</v>
+        <v>75.89</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1514,25 +1517,25 @@
         <v>46</v>
       </c>
       <c r="C45" s="7">
-        <v>1395.8</v>
+        <v>1340.9</v>
       </c>
       <c r="D45" s="7">
-        <v>1764.1</v>
+        <v>1707.4</v>
       </c>
       <c r="E45" s="7">
-        <v>425.7</v>
+        <v>428.9</v>
       </c>
       <c r="F45" s="7">
-        <v>557.6</v>
+        <v>560.4</v>
       </c>
       <c r="G45" s="7">
-        <v>561.7</v>
+        <v>541</v>
       </c>
       <c r="H45" s="7">
-        <v>86.45</v>
+        <v>87.84</v>
       </c>
       <c r="I45" s="8">
-        <v>50</v>
+        <v>66.9</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1540,25 +1543,25 @@
         <v>47</v>
       </c>
       <c r="C46" s="5">
-        <v>1409</v>
+        <v>1395.8</v>
       </c>
       <c r="D46" s="5">
-        <v>1784.6</v>
+        <v>1764.1</v>
       </c>
       <c r="E46" s="5">
-        <v>418.7</v>
+        <v>425.7</v>
       </c>
       <c r="F46" s="5">
-        <v>542.8</v>
+        <v>557.6</v>
       </c>
       <c r="G46" s="5">
-        <v>554.2</v>
+        <v>561.7</v>
       </c>
       <c r="H46" s="5">
-        <v>84.74</v>
+        <v>86.45</v>
       </c>
       <c r="I46" s="6">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1566,25 +1569,25 @@
         <v>48</v>
       </c>
       <c r="C47" s="7">
-        <v>1408.9</v>
+        <v>1409</v>
       </c>
       <c r="D47" s="7">
-        <v>1763.3</v>
+        <v>1784.6</v>
       </c>
       <c r="E47" s="7">
-        <v>421.5</v>
+        <v>418.7</v>
       </c>
       <c r="F47" s="7">
-        <v>545.3</v>
+        <v>542.8</v>
       </c>
       <c r="G47" s="7">
-        <v>541.4</v>
+        <v>554.2</v>
       </c>
       <c r="H47" s="7">
-        <v>82.11</v>
+        <v>84.74</v>
       </c>
       <c r="I47" s="8">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1592,25 +1595,25 @@
         <v>49</v>
       </c>
       <c r="C48" s="5">
-        <v>1428.4</v>
+        <v>1408.9</v>
       </c>
       <c r="D48" s="5">
-        <v>1795.6</v>
+        <v>1763.3</v>
       </c>
       <c r="E48" s="5">
-        <v>419.5</v>
+        <v>421.5</v>
       </c>
       <c r="F48" s="5">
-        <v>538.2</v>
+        <v>545.3</v>
       </c>
       <c r="G48" s="5">
-        <v>537.4</v>
+        <v>541.4</v>
       </c>
       <c r="H48" s="5">
-        <v>77.1</v>
+        <v>82.11</v>
       </c>
       <c r="I48" s="6">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1618,25 +1621,25 @@
         <v>50</v>
       </c>
       <c r="C49" s="7">
-        <v>1402.2</v>
+        <v>1428.4</v>
       </c>
       <c r="D49" s="7">
-        <v>1727.5</v>
+        <v>1795.6</v>
       </c>
       <c r="E49" s="7">
-        <v>406.9</v>
+        <v>419.5</v>
       </c>
       <c r="F49" s="7">
-        <v>518.3</v>
+        <v>538.2</v>
       </c>
       <c r="G49" s="7">
-        <v>474.9</v>
+        <v>537.4</v>
       </c>
       <c r="H49" s="7">
-        <v>63.88</v>
+        <v>77.1</v>
       </c>
       <c r="I49" s="8">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1644,25 +1647,25 @@
         <v>51</v>
       </c>
       <c r="C50" s="5">
-        <v>1419.3</v>
+        <v>1402.2</v>
       </c>
       <c r="D50" s="5">
-        <v>1767.5</v>
+        <v>1727.5</v>
       </c>
       <c r="E50" s="5">
-        <v>405</v>
+        <v>406.9</v>
       </c>
       <c r="F50" s="5">
-        <v>514.1</v>
+        <v>518.3</v>
       </c>
       <c r="G50" s="5">
-        <v>464.9</v>
+        <v>474.9</v>
       </c>
       <c r="H50" s="5">
-        <v>60.64</v>
+        <v>63.88</v>
       </c>
       <c r="I50" s="6">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1670,25 +1673,25 @@
         <v>52</v>
       </c>
       <c r="C51" s="7">
-        <v>1400</v>
+        <v>1419.3</v>
       </c>
       <c r="D51" s="7">
-        <v>1726.3</v>
+        <v>1767.5</v>
       </c>
       <c r="E51" s="7">
-        <v>387.2</v>
+        <v>405</v>
       </c>
       <c r="F51" s="7">
-        <v>497.8</v>
+        <v>514.1</v>
       </c>
       <c r="G51" s="7">
-        <v>430.8</v>
+        <v>464.9</v>
       </c>
       <c r="H51" s="7">
-        <v>55.16</v>
+        <v>60.64</v>
       </c>
       <c r="I51" s="8">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1696,25 +1699,25 @@
         <v>53</v>
       </c>
       <c r="C52" s="5">
-        <v>1389</v>
+        <v>1400</v>
       </c>
       <c r="D52" s="5">
-        <v>1695.9</v>
+        <v>1726.3</v>
       </c>
       <c r="E52" s="5">
-        <v>385.2</v>
+        <v>387.2</v>
       </c>
       <c r="F52" s="5">
-        <v>492.1</v>
+        <v>497.8</v>
       </c>
       <c r="G52" s="5">
-        <v>383.8</v>
+        <v>430.8</v>
       </c>
       <c r="H52" s="5">
-        <v>52.55</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>9</v>
+        <v>55.16</v>
+      </c>
+      <c r="I52" s="6">
+        <v>45</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1722,22 +1725,22 @@
         <v>54</v>
       </c>
       <c r="C53" s="7">
-        <v>1429.8</v>
+        <v>1389</v>
       </c>
       <c r="D53" s="7">
-        <v>1748</v>
+        <v>1695.9</v>
       </c>
       <c r="E53" s="7">
-        <v>380.6</v>
+        <v>385.2</v>
       </c>
       <c r="F53" s="7">
-        <v>483.1</v>
+        <v>492.1</v>
       </c>
       <c r="G53" s="7">
-        <v>401.3</v>
+        <v>383.8</v>
       </c>
       <c r="H53" s="7">
-        <v>51.17</v>
+        <v>52.55</v>
       </c>
       <c r="I53" s="8" t="s">
         <v>9</v>
@@ -1748,22 +1751,22 @@
         <v>55</v>
       </c>
       <c r="C54" s="5">
-        <v>1419.5</v>
+        <v>1429.8</v>
       </c>
       <c r="D54" s="5">
-        <v>1722.3</v>
+        <v>1748</v>
       </c>
       <c r="E54" s="5">
-        <v>365.5</v>
+        <v>380.6</v>
       </c>
       <c r="F54" s="5">
-        <v>460.8</v>
+        <v>483.1</v>
       </c>
       <c r="G54" s="5">
-        <v>389.3</v>
+        <v>401.3</v>
       </c>
       <c r="H54" s="5">
-        <v>42.86</v>
+        <v>51.17</v>
       </c>
       <c r="I54" s="6" t="s">
         <v>9</v>
@@ -1774,22 +1777,22 @@
         <v>56</v>
       </c>
       <c r="C55" s="7">
-        <v>1394.8</v>
+        <v>1419.5</v>
       </c>
       <c r="D55" s="7">
-        <v>1673.3</v>
+        <v>1722.3</v>
       </c>
       <c r="E55" s="7">
-        <v>351.5</v>
+        <v>365.5</v>
       </c>
       <c r="F55" s="7">
-        <v>435.5</v>
+        <v>460.8</v>
       </c>
       <c r="G55" s="7">
-        <v>335.6</v>
+        <v>389.3</v>
       </c>
       <c r="H55" s="7">
-        <v>34.11</v>
+        <v>42.86</v>
       </c>
       <c r="I55" s="8" t="s">
         <v>9</v>
@@ -1800,22 +1803,22 @@
         <v>57</v>
       </c>
       <c r="C56" s="5">
-        <v>1416.5</v>
+        <v>1394.8</v>
       </c>
       <c r="D56" s="5">
-        <v>1713</v>
+        <v>1673.3</v>
       </c>
       <c r="E56" s="5">
-        <v>345.9</v>
+        <v>351.5</v>
       </c>
       <c r="F56" s="5">
-        <v>433.6</v>
+        <v>435.5</v>
       </c>
       <c r="G56" s="5">
-        <v>318.9</v>
+        <v>335.6</v>
       </c>
       <c r="H56" s="5">
-        <v>28.94</v>
+        <v>34.11</v>
       </c>
       <c r="I56" s="6" t="s">
         <v>9</v>
@@ -1826,22 +1829,22 @@
         <v>58</v>
       </c>
       <c r="C57" s="7">
-        <v>1377.9</v>
+        <v>1416.5</v>
       </c>
       <c r="D57" s="7">
-        <v>1641.9</v>
+        <v>1713</v>
       </c>
       <c r="E57" s="7">
-        <v>337.1</v>
+        <v>345.9</v>
       </c>
       <c r="F57" s="7">
-        <v>417.4</v>
+        <v>433.6</v>
       </c>
       <c r="G57" s="7">
-        <v>273.3</v>
+        <v>318.9</v>
       </c>
       <c r="H57" s="7">
-        <v>25.73</v>
+        <v>28.94</v>
       </c>
       <c r="I57" s="8" t="s">
         <v>9</v>
@@ -1852,25 +1855,25 @@
         <v>59</v>
       </c>
       <c r="C58" s="5">
-        <v>1424.2</v>
+        <v>1377.9</v>
       </c>
       <c r="D58" s="5">
-        <v>1698.7</v>
+        <v>1641.9</v>
       </c>
       <c r="E58" s="5">
-        <v>325.5</v>
+        <v>337.1</v>
       </c>
       <c r="F58" s="5">
-        <v>402.8</v>
+        <v>417.4</v>
       </c>
       <c r="G58" s="5">
-        <v>260.4</v>
+        <v>273.3</v>
       </c>
       <c r="H58" s="5">
-        <v>28.39</v>
-      </c>
-      <c r="I58" s="6">
-        <v>50.43</v>
+        <v>25.73</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1878,25 +1881,25 @@
         <v>60</v>
       </c>
       <c r="C59" s="7">
-        <v>1371.4</v>
+        <v>1424.2</v>
       </c>
       <c r="D59" s="7">
-        <v>1621.5</v>
+        <v>1698.7</v>
       </c>
       <c r="E59" s="7">
-        <v>318.3</v>
+        <v>325.5</v>
       </c>
       <c r="F59" s="7">
-        <v>390.6</v>
+        <v>402.8</v>
       </c>
       <c r="G59" s="7">
-        <v>223.2</v>
+        <v>260.4</v>
       </c>
       <c r="H59" s="7">
-        <v>27.68</v>
+        <v>28.39</v>
       </c>
       <c r="I59" s="8">
-        <v>35.16</v>
+        <v>50.43</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1904,25 +1907,25 @@
         <v>61</v>
       </c>
       <c r="C60" s="5">
-        <v>1397.2</v>
+        <v>1371.4</v>
       </c>
       <c r="D60" s="5">
-        <v>1651.9</v>
+        <v>1621.5</v>
       </c>
       <c r="E60" s="5">
-        <v>315.5</v>
+        <v>318.3</v>
       </c>
       <c r="F60" s="5">
-        <v>384.3</v>
+        <v>390.6</v>
       </c>
       <c r="G60" s="5">
-        <v>181.7</v>
+        <v>223.2</v>
       </c>
       <c r="H60" s="5">
-        <v>26.57</v>
+        <v>27.68</v>
       </c>
       <c r="I60" s="6">
-        <v>29.54</v>
+        <v>35.16</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1930,25 +1933,25 @@
         <v>62</v>
       </c>
       <c r="C61" s="7">
-        <v>1402.7</v>
+        <v>1397.2</v>
       </c>
       <c r="D61" s="7">
-        <v>1657.9</v>
+        <v>1651.9</v>
       </c>
       <c r="E61" s="7">
-        <v>311</v>
+        <v>315.5</v>
       </c>
       <c r="F61" s="7">
-        <v>382</v>
+        <v>384.3</v>
       </c>
       <c r="G61" s="7">
-        <v>153.8</v>
+        <v>181.7</v>
       </c>
       <c r="H61" s="7">
-        <v>21.77</v>
+        <v>26.57</v>
       </c>
       <c r="I61" s="8">
-        <v>24.32</v>
+        <v>29.54</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1956,25 +1959,25 @@
         <v>63</v>
       </c>
       <c r="C62" s="5">
-        <v>1387.7</v>
+        <v>1402.7</v>
       </c>
       <c r="D62" s="5">
-        <v>1622.7</v>
+        <v>1657.9</v>
       </c>
       <c r="E62" s="5">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="F62" s="5">
-        <v>369.7</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>9</v>
+        <v>382</v>
+      </c>
+      <c r="G62" s="5">
+        <v>153.8</v>
       </c>
       <c r="H62" s="5">
-        <v>19.82</v>
-      </c>
-      <c r="I62" s="6" t="s">
-        <v>9</v>
+        <v>21.77</v>
+      </c>
+      <c r="I62" s="6">
+        <v>24.32</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1982,22 +1985,22 @@
         <v>64</v>
       </c>
       <c r="C63" s="7">
-        <v>1373.1</v>
+        <v>1387.7</v>
       </c>
       <c r="D63" s="7">
-        <v>1595.3</v>
+        <v>1622.7</v>
       </c>
       <c r="E63" s="7">
-        <v>290.1</v>
+        <v>302</v>
       </c>
       <c r="F63" s="7">
-        <v>354.8</v>
+        <v>369.7</v>
       </c>
       <c r="G63" s="7" t="s">
         <v>9</v>
       </c>
       <c r="H63" s="7">
-        <v>17.61</v>
+        <v>19.82</v>
       </c>
       <c r="I63" s="8" t="s">
         <v>9</v>
@@ -2008,22 +2011,22 @@
         <v>65</v>
       </c>
       <c r="C64" s="5">
-        <v>1398.8</v>
+        <v>1373.1</v>
       </c>
       <c r="D64" s="5">
-        <v>1637.4</v>
+        <v>1595.3</v>
       </c>
       <c r="E64" s="5">
-        <v>271.9</v>
+        <v>290.1</v>
       </c>
       <c r="F64" s="5">
-        <v>332.1</v>
+        <v>354.8</v>
       </c>
       <c r="G64" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H64" s="5">
-        <v>15.39</v>
+        <v>17.61</v>
       </c>
       <c r="I64" s="6" t="s">
         <v>9</v>
@@ -2034,22 +2037,22 @@
         <v>66</v>
       </c>
       <c r="C65" s="7">
-        <v>1372.3</v>
+        <v>1398.8</v>
       </c>
       <c r="D65" s="7">
-        <v>1573.6</v>
+        <v>1637.4</v>
       </c>
       <c r="E65" s="7">
-        <v>269.1</v>
+        <v>271.9</v>
       </c>
       <c r="F65" s="7">
-        <v>326.8</v>
+        <v>332.1</v>
       </c>
       <c r="G65" s="7" t="s">
         <v>9</v>
       </c>
       <c r="H65" s="7">
-        <v>11.01</v>
+        <v>15.39</v>
       </c>
       <c r="I65" s="8" t="s">
         <v>9</v>
@@ -2060,22 +2063,22 @@
         <v>67</v>
       </c>
       <c r="C66" s="5">
-        <v>1362</v>
+        <v>1372.3</v>
       </c>
       <c r="D66" s="5">
-        <v>1552.8</v>
+        <v>1573.6</v>
       </c>
       <c r="E66" s="5">
-        <v>263.4</v>
+        <v>269.1</v>
       </c>
       <c r="F66" s="5">
-        <v>309</v>
+        <v>326.8</v>
       </c>
       <c r="G66" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H66" s="5">
-        <v>7.85</v>
+        <v>11.01</v>
       </c>
       <c r="I66" s="6" t="s">
         <v>9</v>
@@ -2086,22 +2089,22 @@
         <v>68</v>
       </c>
       <c r="C67" s="7">
-        <v>1381.2</v>
+        <v>1362</v>
       </c>
       <c r="D67" s="7">
-        <v>1592.3</v>
+        <v>1552.8</v>
       </c>
       <c r="E67" s="7">
-        <v>266</v>
+        <v>263.4</v>
       </c>
       <c r="F67" s="7">
-        <v>307.1</v>
+        <v>309</v>
       </c>
       <c r="G67" s="7" t="s">
         <v>9</v>
       </c>
       <c r="H67" s="7">
-        <v>7.73</v>
+        <v>7.85</v>
       </c>
       <c r="I67" s="8" t="s">
         <v>9</v>
@@ -2112,22 +2115,22 @@
         <v>69</v>
       </c>
       <c r="C68" s="5">
-        <v>1364.8</v>
+        <v>1381.2</v>
       </c>
       <c r="D68" s="5">
-        <v>1569.6</v>
+        <v>1592.3</v>
       </c>
       <c r="E68" s="5">
-        <v>258.9</v>
+        <v>266</v>
       </c>
       <c r="F68" s="5">
-        <v>297.1</v>
+        <v>307.1</v>
       </c>
       <c r="G68" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H68" s="5">
-        <v>5.43</v>
+        <v>7.73</v>
       </c>
       <c r="I68" s="6" t="s">
         <v>9</v>
@@ -2138,22 +2141,22 @@
         <v>70</v>
       </c>
       <c r="C69" s="7">
-        <v>1363.4</v>
+        <v>1364.8</v>
       </c>
       <c r="D69" s="7">
-        <v>1567.6</v>
+        <v>1569.6</v>
       </c>
       <c r="E69" s="7">
-        <v>256.7</v>
+        <v>258.9</v>
       </c>
       <c r="F69" s="7">
-        <v>294.5</v>
+        <v>297.1</v>
       </c>
       <c r="G69" s="7" t="s">
         <v>9</v>
       </c>
       <c r="H69" s="7">
-        <v>4.52</v>
+        <v>5.43</v>
       </c>
       <c r="I69" s="8" t="s">
         <v>9</v>
@@ -2164,22 +2167,22 @@
         <v>71</v>
       </c>
       <c r="C70" s="5">
-        <v>1354</v>
+        <v>1363.4</v>
       </c>
       <c r="D70" s="5">
-        <v>1562.1</v>
+        <v>1567.6</v>
       </c>
       <c r="E70" s="5">
-        <v>248.8</v>
+        <v>256.7</v>
       </c>
       <c r="F70" s="5">
-        <v>284.6</v>
+        <v>294.5</v>
       </c>
       <c r="G70" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H70" s="5">
-        <v>3.38</v>
+        <v>4.52</v>
       </c>
       <c r="I70" s="6" t="s">
         <v>9</v>
@@ -2190,25 +2193,25 @@
         <v>72</v>
       </c>
       <c r="C71" s="7">
-        <v>1332</v>
+        <v>1354</v>
       </c>
       <c r="D71" s="7">
-        <v>1527.7</v>
+        <v>1562.1</v>
       </c>
       <c r="E71" s="7">
-        <v>246.6</v>
+        <v>248.8</v>
       </c>
       <c r="F71" s="7">
-        <v>279.8</v>
+        <v>284.6</v>
       </c>
       <c r="G71" s="7" t="s">
         <v>9</v>
       </c>
       <c r="H71" s="7">
-        <v>2.92</v>
-      </c>
-      <c r="I71" s="8">
-        <v>8.62</v>
+        <v>3.38</v>
+      </c>
+      <c r="I71" s="8" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="72" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -2216,25 +2219,25 @@
         <v>73</v>
       </c>
       <c r="C72" s="5">
-        <v>1329.4</v>
+        <v>1332</v>
       </c>
       <c r="D72" s="5">
-        <v>1528.2</v>
+        <v>1527.7</v>
       </c>
       <c r="E72" s="5">
-        <v>240.4</v>
+        <v>246.6</v>
       </c>
       <c r="F72" s="5">
-        <v>274.5</v>
+        <v>279.8</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H72" s="5">
-        <v>3.05</v>
-      </c>
-      <c r="I72" s="6" t="s">
-        <v>9</v>
+        <v>2.92</v>
+      </c>
+      <c r="I72" s="6">
+        <v>8.62</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -2242,22 +2245,22 @@
         <v>74</v>
       </c>
       <c r="C73" s="7">
-        <v>1318.3</v>
+        <v>1329.4</v>
       </c>
       <c r="D73" s="7">
-        <v>1516.3</v>
+        <v>1528.2</v>
       </c>
       <c r="E73" s="7">
-        <v>234</v>
+        <v>240.4</v>
       </c>
       <c r="F73" s="7">
-        <v>269.5</v>
+        <v>274.5</v>
       </c>
       <c r="G73" s="7" t="s">
         <v>9</v>
       </c>
       <c r="H73" s="7">
-        <v>2.24</v>
+        <v>3.05</v>
       </c>
       <c r="I73" s="8" t="s">
         <v>9</v>
@@ -2268,22 +2271,22 @@
         <v>75</v>
       </c>
       <c r="C74" s="5">
-        <v>1290.8</v>
+        <v>1318.3</v>
       </c>
       <c r="D74" s="5">
-        <v>1458.3</v>
+        <v>1516.3</v>
       </c>
       <c r="E74" s="5">
-        <v>231.6</v>
+        <v>234</v>
       </c>
       <c r="F74" s="5">
-        <v>266.3</v>
+        <v>269.5</v>
       </c>
       <c r="G74" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H74" s="5">
-        <v>1.84</v>
+        <v>2.24</v>
       </c>
       <c r="I74" s="6" t="s">
         <v>9</v>
@@ -2294,22 +2297,22 @@
         <v>76</v>
       </c>
       <c r="C75" s="7">
-        <v>1308.5</v>
+        <v>1290.8</v>
       </c>
       <c r="D75" s="7">
-        <v>1494.9</v>
+        <v>1458.3</v>
       </c>
       <c r="E75" s="7">
-        <v>225.3</v>
+        <v>231.6</v>
       </c>
       <c r="F75" s="7">
-        <v>257.1</v>
+        <v>266.3</v>
       </c>
       <c r="G75" s="7" t="s">
         <v>9</v>
       </c>
       <c r="H75" s="7">
-        <v>1.54</v>
+        <v>1.84</v>
       </c>
       <c r="I75" s="8" t="s">
         <v>9</v>
@@ -2320,22 +2323,22 @@
         <v>77</v>
       </c>
       <c r="C76" s="5">
-        <v>1291.6</v>
+        <v>1308.5</v>
       </c>
       <c r="D76" s="5">
-        <v>1473.1</v>
+        <v>1494.9</v>
       </c>
       <c r="E76" s="5">
-        <v>227.6</v>
+        <v>225.3</v>
       </c>
       <c r="F76" s="5">
-        <v>256.4</v>
+        <v>257.1</v>
       </c>
       <c r="G76" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H76" s="5">
-        <v>1.31</v>
+        <v>1.54</v>
       </c>
       <c r="I76" s="6" t="s">
         <v>9</v>
@@ -2346,22 +2349,22 @@
         <v>78</v>
       </c>
       <c r="C77" s="7">
-        <v>1278.5</v>
+        <v>1291.6</v>
       </c>
       <c r="D77" s="7">
-        <v>1440.9</v>
+        <v>1473.1</v>
       </c>
       <c r="E77" s="7">
-        <v>220.9</v>
+        <v>227.6</v>
       </c>
       <c r="F77" s="7">
-        <v>249.5</v>
+        <v>256.4</v>
       </c>
       <c r="G77" s="7" t="s">
         <v>9</v>
       </c>
       <c r="H77" s="7">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="I77" s="8" t="s">
         <v>9</v>
@@ -2372,22 +2375,22 @@
         <v>79</v>
       </c>
       <c r="C78" s="5">
-        <v>1268.1</v>
+        <v>1278.5</v>
       </c>
       <c r="D78" s="5">
-        <v>1424.8</v>
+        <v>1440.9</v>
       </c>
       <c r="E78" s="5">
-        <v>218.7</v>
+        <v>220.9</v>
       </c>
       <c r="F78" s="5">
-        <v>243.6</v>
+        <v>249.5</v>
       </c>
       <c r="G78" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H78" s="5">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="I78" s="6" t="s">
         <v>9</v>
@@ -2398,22 +2401,22 @@
         <v>80</v>
       </c>
       <c r="C79" s="7">
-        <v>1234.4</v>
+        <v>1268.1</v>
       </c>
       <c r="D79" s="7">
-        <v>1376.8</v>
+        <v>1424.8</v>
       </c>
       <c r="E79" s="7">
-        <v>211.2</v>
+        <v>218.7</v>
       </c>
       <c r="F79" s="7">
-        <v>233.1</v>
+        <v>243.6</v>
       </c>
       <c r="G79" s="7" t="s">
         <v>9</v>
       </c>
       <c r="H79" s="7">
-        <v>660000e-6</v>
+        <v>1.05</v>
       </c>
       <c r="I79" s="8" t="s">
         <v>9</v>
@@ -2424,16 +2427,16 @@
         <v>81</v>
       </c>
       <c r="C80" s="5">
-        <v>1194</v>
+        <v>1234.4</v>
       </c>
       <c r="D80" s="5">
-        <v>1332.3</v>
+        <v>1376.8</v>
       </c>
       <c r="E80" s="5">
-        <v>210.5</v>
+        <v>211.2</v>
       </c>
       <c r="F80" s="5">
-        <v>231.8</v>
+        <v>233.1</v>
       </c>
       <c r="G80" s="5" t="s">
         <v>9</v>
@@ -2446,50 +2449,77 @@
       </c>
     </row>
     <row r="81" s="1" customFormat="1" ht="19.7321" customHeight="1">
-      <c r="B81" s="9" t="s">
+      <c r="B81" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C81" s="10">
+      <c r="C81" s="7">
+        <v>1194</v>
+      </c>
+      <c r="D81" s="7">
+        <v>1332.3</v>
+      </c>
+      <c r="E81" s="7">
+        <v>210.5</v>
+      </c>
+      <c r="F81" s="7">
+        <v>231.8</v>
+      </c>
+      <c r="G81" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H81" s="7">
+        <v>660000e-6</v>
+      </c>
+      <c r="I81" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" s="1" customFormat="1" ht="19.7321" customHeight="1">
+      <c r="B82" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C82" s="10">
         <v>1187.5</v>
       </c>
-      <c r="D81" s="10">
+      <c r="D82" s="10">
         <v>1318.9</v>
       </c>
-      <c r="E81" s="10">
+      <c r="E82" s="10">
         <v>208.5</v>
       </c>
-      <c r="F81" s="10">
+      <c r="F82" s="10">
         <v>225.6</v>
       </c>
-      <c r="G81" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H81" s="10">
+      <c r="G82" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H82" s="10">
         <v>690000e-6</v>
       </c>
-      <c r="I81" s="11">
+      <c r="I82" s="11">
         <v>2.35</v>
       </c>
     </row>
-    <row r="82" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
-    <row r="83" s="1" customFormat="1" ht="118.9259" customHeight="1">
-      <c r="B83" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="C83" s="14"/>
-      <c r="D83" s="14"/>
-      <c r="E83" s="14"/>
-      <c r="F83" s="14"/>
-      <c r="G83" s="14"/>
-      <c r="H83" s="14"/>
-      <c r="I83" s="14"/>
-      <c r="J83" s="14"/>
-    </row>
+    <row r="83" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
+    <row r="84" s="1" customFormat="1" ht="118.9259" customHeight="1">
+      <c r="B84" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C84" s="14"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="14"/>
+      <c r="F84" s="14"/>
+      <c r="G84" s="14"/>
+      <c r="H84" s="14"/>
+      <c r="I84" s="14"/>
+      <c r="J84" s="14"/>
+    </row>
+    <row r="85" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B2:K2"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B83:J83"/>
+    <mergeCell ref="B84:J84"/>
   </mergeCells>
   <pageSetup paperSize="120" scale="100" orientation="landscape"/>
   <headerFooter alignWithMargins="0"/>
